--- a/Result/profitability/3356.xlsx
+++ b/Result/profitability/3356.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.94</v>
       </c>
       <c r="M2" t="n">
-        <v>1.69</v>
+        <v>2.36875</v>
       </c>
       <c r="N2" t="n">
-        <v>51.61625</v>
+        <v>51.53</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>3.56</v>
       </c>
       <c r="M3" t="n">
-        <v>2.11625</v>
+        <v>2.5625</v>
       </c>
       <c r="N3" t="n">
-        <v>54.105</v>
+        <v>54.12375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -801,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>3.53</v>
       </c>
       <c r="M4" t="n">
-        <v>2.30625</v>
+        <v>3.21875</v>
       </c>
       <c r="N4" t="n">
-        <v>56.72375</v>
+        <v>56.36</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>97.3</v>
@@ -1018,10 +1018,10 @@
         <v>2.46</v>
       </c>
       <c r="M5" t="n">
-        <v>2.82875</v>
+        <v>3.325</v>
       </c>
       <c r="N5" t="n">
-        <v>58.85124999999999</v>
+        <v>58.4825</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>2.31</v>
       </c>
       <c r="M6" t="n">
-        <v>2.91625</v>
+        <v>3.205</v>
       </c>
       <c r="N6" t="n">
-        <v>61.21</v>
+        <v>60.91374999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.73</v>
       </c>
       <c r="M7" t="n">
-        <v>2.72375</v>
+        <v>3.04</v>
       </c>
       <c r="N7" t="n">
-        <v>63.3875</v>
+        <v>63.17125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>2.58625</v>
+        <v>3.0075</v>
       </c>
       <c r="N8" t="n">
-        <v>65.31999999999999</v>
+        <v>65.08875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>2.58125</v>
       </c>
       <c r="N9" t="n">
-        <v>67.66624999999999</v>
+        <v>67.66625000000001</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>2.01125</v>
       </c>
       <c r="N12" t="n">
-        <v>66.71375</v>
+        <v>66.71374999999999</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>1.78125</v>
       </c>
       <c r="N13" t="n">
-        <v>65.90124999999999</v>
+        <v>65.90125</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3356</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>280</v>
+      </c>
+      <c r="D75" t="n">
+        <v>146</v>
+      </c>
+      <c r="E75" t="n">
+        <v>134</v>
+      </c>
+      <c r="F75" t="n">
+        <v>47.78</v>
+      </c>
+      <c r="G75" t="n">
+        <v>6</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>452</v>
+      </c>
+      <c r="J75" t="n">
+        <v>458</v>
+      </c>
+      <c r="K75" t="n">
+        <v>446</v>
+      </c>
+      <c r="L75" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N75" t="n">
+        <v>49.32375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.524886877828054</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.850000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03727584122506555</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.46583850931677</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.949999999999996</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.05815099546619351</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
